--- a/data/trans_dic/P6901-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,89; 91,6</t>
+          <t>78,48; 91,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,91; 83,15</t>
+          <t>58,56; 82,93</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>63,5; 88,25</t>
+          <t>62,67; 87,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68,19; 95,48</t>
+          <t>69,65; 96,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>70,04; 94,71</t>
+          <t>71,17; 94,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,59; 84,24</t>
+          <t>56,64; 85,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,54; 100,0</t>
+          <t>67,45; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>34,3; 98,22</t>
+          <t>32,32; 98,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78,93; 90,94</t>
+          <t>78,88; 90,71</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62,31; 81,02</t>
+          <t>63,13; 81,66</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69,43; 89,5</t>
+          <t>69,17; 89,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,7; 93,21</t>
+          <t>55,25; 93,13</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>70,85; 81,21</t>
+          <t>71,31; 81,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,7; 81,37</t>
+          <t>70,06; 81,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>72,05; 83,26</t>
+          <t>71,56; 82,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,08; 83,98</t>
+          <t>72,16; 83,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>75,48; 89,16</t>
+          <t>74,86; 88,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,04; 91,1</t>
+          <t>77,68; 90,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>84,55; 95,11</t>
+          <t>83,51; 94,88</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,36; 90,86</t>
+          <t>79,61; 90,37</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,07; 82,4</t>
+          <t>73,84; 82,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74,67; 83,75</t>
+          <t>74,92; 83,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78,27; 86,35</t>
+          <t>77,52; 86,12</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,16; 85,45</t>
+          <t>77,5; 85,44</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,8; 64,55</t>
+          <t>40,28; 65,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>53,55; 81,96</t>
+          <t>54,27; 81,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45,62; 72,24</t>
+          <t>44,56; 71,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34,34; 61,07</t>
+          <t>33,73; 61,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>51,95; 75,42</t>
+          <t>53,03; 75,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>45,5; 75,26</t>
+          <t>44,59; 74,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,3; 83,75</t>
+          <t>63,06; 84,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,03; 70,64</t>
+          <t>51,47; 70,67</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,59; 66,89</t>
+          <t>49,97; 67,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>54,41; 74,32</t>
+          <t>53,51; 74,52</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58,5; 74,19</t>
+          <t>58,52; 75,5</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47,68; 62,68</t>
+          <t>47,17; 63,37</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,83; 78,8</t>
+          <t>71,04; 78,81</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>68,91; 79,21</t>
+          <t>69,55; 79,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>69,31; 79,15</t>
+          <t>68,72; 79,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67,03; 77,59</t>
+          <t>67,24; 77,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,88; 83,08</t>
+          <t>71,9; 83,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,79; 83,76</t>
+          <t>71,63; 83,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,06; 88,9</t>
+          <t>79,65; 89,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>72,1; 83,98</t>
+          <t>71,93; 84,23</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,42; 79,35</t>
+          <t>72,43; 78,97</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71,72; 79,12</t>
+          <t>71,94; 79,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74,76; 81,75</t>
+          <t>74,59; 81,96</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,56; 79,66</t>
+          <t>71,73; 80,18</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores en la espalda (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87795; 101937</t>
+          <t>87337; 102176</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34620; 48866</t>
+          <t>34414; 48733</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35294; 49051</t>
+          <t>34830; 48774</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>19920; 27894</t>
+          <t>20347; 28057</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26311; 35580</t>
+          <t>26737; 35650</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21467; 31957</t>
+          <t>21487; 32568</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11994; 18024</t>
+          <t>12158; 18024</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8571; 24540</t>
+          <t>8075; 24569</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>117492; 135364</t>
+          <t>117413; 135030</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60260; 78350</t>
+          <t>61044; 78969</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>51103; 65876</t>
+          <t>50914; 65665</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29646; 50519</t>
+          <t>29945; 50478</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>203288; 233037</t>
+          <t>204623; 233377</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>152345; 180427</t>
+          <t>155355; 181617</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>165270; 190977</t>
+          <t>164152; 190198</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>175089; 201190</t>
+          <t>172889; 200276</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89492; 105719</t>
+          <t>88757; 105441</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>100559; 118913</t>
+          <t>101392; 118696</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>105320; 118473</t>
+          <t>104027; 118191</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>189169; 216576</t>
+          <t>189760; 215422</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>300378; 334149</t>
+          <t>299417; 334411</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>263045; 295028</t>
+          <t>263923; 294784</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>277036; 305622</t>
+          <t>274368; 304810</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>368779; 408398</t>
+          <t>370401; 408347</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30967; 47819</t>
+          <t>29840; 48813</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>24682; 37775</t>
+          <t>25012; 37521</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28981; 45891</t>
+          <t>28307; 45589</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23878; 42460</t>
+          <t>23452; 42455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33237; 48254</t>
+          <t>33932; 48610</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20566; 34013</t>
+          <t>20155; 33719</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46659; 61732</t>
+          <t>46479; 62002</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46278; 64067</t>
+          <t>46681; 64094</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>68468; 92351</t>
+          <t>68991; 92872</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>49665; 67840</t>
+          <t>48842; 68027</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80289; 101811</t>
+          <t>80315; 103615</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>76393; 100426</t>
+          <t>75580; 101526</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>334550; 372165</t>
+          <t>335509; 372213</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>225061; 258703</t>
+          <t>227148; 259487</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>241547; 275825</t>
+          <t>239483; 276137</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>226773; 262490</t>
+          <t>227499; 262476</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>158216; 182869</t>
+          <t>158264; 183829</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>153383; 178952</t>
+          <t>153048; 177544</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>171011; 192299</t>
+          <t>172284; 193490</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>255263; 297339</t>
+          <t>254685; 298217</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>501482; 549421</t>
+          <t>501537; 546815</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>387473; 427464</t>
+          <t>388684; 429310</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>422253; 461718</t>
+          <t>421275; 462913</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>495487; 551541</t>
+          <t>496609; 555133</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6901-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P6901-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>86,17%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,84%</t>
+          <t>88,72%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>78,48; 91,81</t>
+          <t>78,13; 91,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>58,56; 82,93</t>
+          <t>59,27; 82,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,67; 87,75</t>
+          <t>63,58; 88,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69,65; 96,04</t>
+          <t>70,85; 94,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>71,17; 94,9</t>
+          <t>69,56; 94,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,64; 85,85</t>
+          <t>56,24; 85,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>67,45; 100,0</t>
+          <t>66,44; 100,0</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>32,32; 98,33</t>
+          <t>79,6; 97,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>78,88; 90,71</t>
+          <t>79,3; 90,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63,13; 81,66</t>
+          <t>62,09; 80,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>69,17; 89,21</t>
+          <t>69,25; 88,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>55,25; 93,13</t>
+          <t>79,82; 94,6</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>78,5%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,35%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,31; 81,33</t>
+          <t>71,09; 80,92</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>70,06; 81,91</t>
+          <t>69,73; 81,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,56; 82,92</t>
+          <t>71,88; 82,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72,16; 83,59</t>
+          <t>75,58; 85,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>74,86; 88,93</t>
+          <t>76,5; 89,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>77,68; 90,93</t>
+          <t>77,37; 90,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>83,51; 94,88</t>
+          <t>84,41; 95,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,61; 90,37</t>
+          <t>76,9; 86,32</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>73,84; 82,47</t>
+          <t>74,14; 82,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74,92; 83,68</t>
+          <t>74,95; 83,67</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>77,52; 86,12</t>
+          <t>78,03; 86,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>77,5; 85,44</t>
+          <t>77,62; 84,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>48,36%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>57,12%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>40,28; 65,9</t>
+          <t>41,33; 66,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54,27; 81,41</t>
+          <t>53,7; 80,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>44,56; 71,76</t>
+          <t>45,63; 72,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>33,73; 61,06</t>
+          <t>34,37; 62,38</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>53,03; 75,97</t>
+          <t>51,81; 76,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,59; 74,61</t>
+          <t>44,25; 74,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,06; 84,12</t>
+          <t>63,25; 82,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,47; 70,67</t>
+          <t>55,17; 72,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>49,97; 67,27</t>
+          <t>49,23; 66,84</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>53,51; 74,52</t>
+          <t>54,18; 74,18</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>58,52; 75,5</t>
+          <t>58,6; 75,28</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>47,17; 63,37</t>
+          <t>49,54; 65,58</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>77,98%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>71,04; 78,81</t>
+          <t>70,82; 79,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>69,55; 79,45</t>
+          <t>68,82; 79,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,72; 79,24</t>
+          <t>69,02; 79,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>67,24; 77,58</t>
+          <t>69,17; 78,97</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>71,9; 83,51</t>
+          <t>72,29; 83,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,63; 83,1</t>
+          <t>70,59; 83,34</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,65; 89,46</t>
+          <t>79,3; 89,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>71,93; 84,23</t>
+          <t>73,12; 81,15</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>72,43; 78,97</t>
+          <t>72,44; 79,05</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>71,94; 79,46</t>
+          <t>71,79; 79,24</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>74,59; 81,96</t>
+          <t>74,23; 81,85</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>71,73; 80,18</t>
+          <t>72,35; 78,76</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25173</t>
+          <t>31374</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>18644</t>
+          <t>22497</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>43818</t>
+          <t>53871</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>87337; 102176</t>
+          <t>86943; 101949</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>34414; 48733</t>
+          <t>34828; 48239</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34830; 48774</t>
+          <t>35337; 49050</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>20347; 28057</t>
+          <t>25658; 34335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>26737; 35650</t>
+          <t>26134; 35431</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>21487; 32568</t>
+          <t>21333; 32603</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12158; 18024</t>
+          <t>11976; 18024</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8075; 24569</t>
+          <t>19507; 23897</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>117413; 135030</t>
+          <t>118036; 135383</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61044; 78969</t>
+          <t>60041; 77521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>50914; 65665</t>
+          <t>50972; 65453</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29945; 50478</t>
+          <t>48467; 57442</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188079</t>
+          <t>217924</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>201181</t>
+          <t>181181</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>389260</t>
+          <t>399105</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>204623; 233377</t>
+          <t>203983; 232199</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>155355; 181617</t>
+          <t>154611; 181246</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164152; 190198</t>
+          <t>164877; 190203</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>172889; 200276</t>
+          <t>203861; 230330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>88757; 105441</t>
+          <t>90708; 106381</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>101392; 118696</t>
+          <t>100988; 118566</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>104027; 118191</t>
+          <t>105142; 118550</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>189760; 215422</t>
+          <t>169842; 190656</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>299417; 334411</t>
+          <t>300649; 334399</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>263923; 294784</t>
+          <t>264011; 294746</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>274368; 304810</t>
+          <t>276202; 304596</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>370401; 408347</t>
+          <t>380821; 412930</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>32540</t>
+          <t>37604</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56269</t>
+          <t>63602</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>88809</t>
+          <t>101206</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>29840; 48813</t>
+          <t>30617; 49162</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>25012; 37521</t>
+          <t>24750; 37287</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28307; 45589</t>
+          <t>28990; 45798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23452; 42455</t>
+          <t>26726; 48511</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33932; 48610</t>
+          <t>33150; 48854</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20155; 33719</t>
+          <t>20001; 33754</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>46479; 62002</t>
+          <t>46621; 61152</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46681; 64094</t>
+          <t>54844; 72178</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>68991; 92872</t>
+          <t>67961; 92275</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>48842; 68027</t>
+          <t>49460; 67714</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>80315; 103615</t>
+          <t>80414; 103306</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>75580; 101526</t>
+          <t>87777; 116187</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>245792</t>
+          <t>286901</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>276095</t>
+          <t>267280</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>521887</t>
+          <t>554182</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>335509; 372213</t>
+          <t>334494; 373635</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>227148; 259487</t>
+          <t>224757; 258165</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>239483; 276137</t>
+          <t>240530; 276712</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>227499; 262476</t>
+          <t>265412; 303035</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>158264; 183829</t>
+          <t>159126; 183386</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>153048; 177544</t>
+          <t>150830; 178059</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>172284; 193490</t>
+          <t>171528; 194382</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>254685; 298217</t>
+          <t>252114; 279792</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>501537; 546815</t>
+          <t>501604; 547366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>388684; 429310</t>
+          <t>387854; 428116</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>421275; 462913</t>
+          <t>419219; 462268</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>496609; 555133</t>
+          <t>527098; 573733</t>
         </is>
       </c>
     </row>
